--- a/public/sap-reporting/expansion-150-downloads/EXT-FI18-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI18-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rdec4031c2dca46f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rc79e4663c02b4e5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R01570174567a4d22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rfbff7f25ee144b4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R06434de184d640af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rd8ffc474f93b4cab"/>
   </x:sheets>
 </x:workbook>
 </file>
